--- a/game_config/Datas/MonsterConfig.xlsx
+++ b/game_config/Datas/MonsterConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\gitee\TiangZ\game_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07C30DD3-2DFB-45DB-9125-0A0957125875}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{809FF718-D350-486F-AAC0-3E4292CCBECB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-1320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ItemConfig" sheetId="1" r:id="rId1"/>
@@ -668,7 +668,7 @@
         <v>34</v>
       </c>
       <c r="E5">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="F5">
         <v>100</v>
@@ -706,7 +706,7 @@
         <v>36</v>
       </c>
       <c r="E6">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="G6">
         <v>12</v>

--- a/game_config/Datas/MonsterConfig.xlsx
+++ b/game_config/Datas/MonsterConfig.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t>##var</t>
   </si>
@@ -136,6 +136,12 @@
   </si>
   <si>
     <t>monster/wolf</t>
+  </si>
+  <si>
+    <t>drop_table_id</t>
+  </si>
+  <si>
+    <t>掉落表配置ID；0表示不生成掉落</t>
   </si>
 </sst>
 </file>
@@ -482,7 +488,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="12" customWidth="1"/>
@@ -491,9 +497,10 @@
     <col min="7" max="7" width="14" customWidth="1"/>
     <col min="12" max="12" width="13" customWidth="1"/>
     <col min="13" max="13" width="16" customWidth="1"/>
+    <col min="14" max="14" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -533,8 +540,11 @@
       <c r="M1" t="s">
         <v>12</v>
       </c>
+      <c r="N1" t="s">
+        <v>37</v>
+      </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -574,8 +584,11 @@
       <c r="M2" t="s">
         <v>14</v>
       </c>
+      <c r="N2" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -615,8 +628,11 @@
       <c r="M3" t="s">
         <v>19</v>
       </c>
+      <c r="N3" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -656,8 +672,11 @@
       <c r="M4" t="s">
         <v>32</v>
       </c>
+      <c r="N4" t="s">
+        <v>38</v>
+      </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B5">
         <v>1</v>
       </c>
@@ -694,8 +713,11 @@
       <c r="M5">
         <v>10</v>
       </c>
+      <c r="N5">
+        <v>1</v>
+      </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B6">
         <v>2</v>
       </c>
@@ -728,6 +750,9 @@
       </c>
       <c r="M6">
         <v>10</v>
+      </c>
+      <c r="N6">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/game_config/Datas/MonsterConfig.xlsx
+++ b/game_config/Datas/MonsterConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\gitee\TiangZ\game_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{809FF718-D350-486F-AAC0-3E4292CCBECB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F2BFBCD-24E2-498E-9488-90AE86E0596D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-1320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="41">
   <si>
     <t>##var</t>
   </si>
@@ -142,6 +142,14 @@
   </si>
   <si>
     <t>掉落表配置ID；0表示不生成掉落</t>
+  </si>
+  <si>
+    <t>试炼守卫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>monster/boss</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -488,7 +496,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="12" customWidth="1"/>
@@ -755,6 +763,47 @@
         <v>2</v>
       </c>
     </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7">
+        <v>900</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>18</v>
+      </c>
+      <c r="H7">
+        <v>4</v>
+      </c>
+      <c r="I7">
+        <v>2.8</v>
+      </c>
+      <c r="J7">
+        <v>1600</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>3600</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/game_config/Datas/MonsterConfig.xlsx
+++ b/game_config/Datas/MonsterConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\gitee\TiangZ\game_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F2BFBCD-24E2-498E-9488-90AE86E0596D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8423FA4-B8B9-44FA-821B-413CD5705B3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-1320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ItemConfig" sheetId="1" r:id="rId1"/>
@@ -801,7 +801,7 @@
         <v>3600</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
